--- a/观察池.xlsx
+++ b/观察池.xlsx
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
   <si>
     <t>序号</t>
   </si>
@@ -402,37 +402,43 @@
     <t>老凤祥B</t>
   </si>
   <si>
+    <t>sh900905</t>
+  </si>
+  <si>
     <t>古井贡B</t>
   </si>
   <si>
+    <t>sz200596</t>
+  </si>
+  <si>
     <t>泡泡玛特</t>
   </si>
   <si>
-    <t>hk9992</t>
+    <t>hk09992</t>
   </si>
   <si>
     <t>蜜雪集团</t>
   </si>
   <si>
-    <t>hk2097</t>
+    <t>hk02097</t>
   </si>
   <si>
     <t>中国船舶租赁</t>
   </si>
   <si>
-    <t>hk3877</t>
+    <t>hk03877</t>
   </si>
   <si>
     <t>老铺黄金</t>
   </si>
   <si>
-    <t>hk6181</t>
+    <t>hk06181</t>
   </si>
   <si>
     <t>茶百道</t>
   </si>
   <si>
-    <t>hk2555</t>
+    <t>hk02555</t>
   </si>
 </sst>
 </file>
@@ -3341,8 +3347,8 @@
       <c r="K28" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="L28" s="7">
-        <v>900905</v>
+      <c r="L28" s="7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:37">
@@ -3357,10 +3363,10 @@
         <v>42</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L29" s="7">
-        <v>200596</v>
+        <v>106</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:37">
@@ -3375,10 +3381,10 @@
         <v>126</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:37">
@@ -3393,10 +3399,10 @@
         <v>189</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:37">
@@ -3411,10 +3417,10 @@
         <v>1.89</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:12">
@@ -3429,10 +3435,10 @@
         <v>315</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:12">
@@ -3447,10 +3453,10 @@
         <v>3.15</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
